--- a/tests/SafeOpenXml.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R744598b11e2c4298"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ad7e7d4887a4c34"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R6f6fea80a48247de"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1758e6da58e54fa7"/>
   </x:pivotCaches>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/PivotTableRowAndColumn/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/PivotTableRowAndColumn/output.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3ad7e7d4887a4c34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R8da5e5258c2140df"/>
   </x:sheets>
   <x:pivotCaches>
-    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="R1758e6da58e54fa7"/>
+    <x:pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="0" r:id="Rc260d92a977a458e"/>
   </x:pivotCaches>
 </x:workbook>
 </file>
